--- a/result/work_1.xlsx
+++ b/result/work_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mylife_yanjiu\project\concolic_on_RTL\result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72ADDB37-BE60-4D90-BFC1-8DAAF09A1B41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CA402D7-3B8C-4570-ABB8-B92EC6F73F8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19103" yWindow="-3090" windowWidth="24195" windowHeight="14475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/result/work_1.xlsx
+++ b/result/work_1.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mylife_yanjiu\project\concolic_on_RTL\result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CA402D7-3B8C-4570-ABB8-B92EC6F73F8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A519EEF7-FBBE-4B0F-9150-A3F8F83BFC67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19103" yWindow="-3090" windowWidth="24195" windowHeight="14475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19103" yWindow="-3090" windowWidth="24195" windowHeight="14475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="119">
   <si>
     <t>ITC99</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -216,6 +217,290 @@
   </si>
   <si>
     <t>['59,0,1,7,0', '32,0,3,1,1', '59,0,1,5,1', '59,0,1,8,1', '63,1,0,0', '59,0,1,5', '69,1,0,1', '60,1,0,0,1', '59,0,1,6,0', '59,0,1,6,1', '59,0,1,8', '64,1,0,0,1,1', '59,0,1,6,0,1', '63,1,0,0,1', '59,0,1,6', '67,1,1', '69,1,0,0,1', '59,0,1,6,0,0', '60,1,0,1', '59,0,1,7', '59,0,1,7,1', '61,1,1']</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>b11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>18的覆盖效果较差</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对数据流的分析不足</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>b14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据流分析不足</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>case3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>节点不能覆盖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>周期分析问题</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>复杂路径的覆盖能力不足</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>节点73能覆盖，而76不行？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据流能力受限导致覆盖不到</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AES-T1100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>能覆盖到木马节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>耗时很长</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>待测模块</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>序号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Target（难覆盖）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否覆盖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DATE 18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本方法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间/ms</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,1,0,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1,0,0,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,1,0,1,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>×</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间计算：静态解析+随机执行+（动态执行+求解）*迭代次数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.15+14+175.9+2.73+569.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.044+0.84+11.78+15.64</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>展开周期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.15+14+175.9+2.55+165.7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.044+0.84+11.78+13.6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.15+34.54+175.9+7.78+164.4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.044+1.07+11.78+13.6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1,0,3,1,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1,0,3,1,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1,0,7,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1,0,8,0,0,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0+3.74+12.88+6.964+11.14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.24+285.9+179.6+20.71+177.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.24+61,1+222.7+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0+2.9+15.7+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icache</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8,1,0,3,0,0,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8,1,0,3,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8,1,0,2,1,1,0,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.9+45.8+239.7+56.9+258.6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.012+2.89+13.1+19.5+22.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.9+32+239.7+19.7+238.6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.012+2.86+13.1+18.8+15.8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第一个节点顺道覆盖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.012+2.1+12.7+18.6+12.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.9+19.5+240.9+33.7+267.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>21,1,0,0,1,1,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>25,1,0,0,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>随机覆盖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9.28+167.1+171.4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0+4.05+22.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>25,1,0,0,5,1,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>25,1,0,0,4,1,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AES-T1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>86.7+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5.14s+10s</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wb_conmaxT200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wb_conmaxT300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.1+3+217.4+31+202.7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3+0+13.6+18.4+14.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>59,0,1,3,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>59,0,1,5,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>59,0,1,7,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>59,0,1,6,0,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15min+</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -247,7 +532,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -284,11 +569,40 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -303,6 +617,27 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -585,7 +920,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr defaultColWidth="12.77734375" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="12.77734375" style="1"/>
@@ -1154,8 +1489,695 @@
         <v>23.312000000000001</v>
       </c>
     </row>
+    <row r="28" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17A3E605-A7A4-4A43-8D4B-58BBFEC21B52}">
+  <dimension ref="A1:K28"/>
+  <sheetFormatPr defaultColWidth="16.77734375" defaultRowHeight="28.05" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="16.77734375" style="1"/>
+    <col min="3" max="3" width="20" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.77734375" style="6"/>
+    <col min="5" max="6" width="16.77734375" style="1"/>
+    <col min="7" max="7" width="16.77734375" style="2"/>
+    <col min="8" max="9" width="16.77734375" style="1"/>
+    <col min="10" max="10" width="16.77734375" style="2"/>
+    <col min="11" max="11" width="39.5546875" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="16.77734375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" s="9"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="9">
+        <v>1</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="6">
+        <v>20</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="6">
+        <v>20</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" s="3" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="12"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" s="7">
+        <v>20</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="11">
+        <v>2</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6" s="6">
+        <v>100</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="9"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D7" s="6">
+        <v>100</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8" s="6">
+        <v>100</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" s="6">
+        <v>100</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="9">
+        <v>3</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D10" s="6">
+        <v>50</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="6">
+        <v>50</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D12" s="6">
+        <v>50</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D13" s="6">
+        <v>50</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="9">
+        <v>4</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="6">
+        <v>20</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D15" s="6">
+        <v>40</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" s="1">
+        <v>18.829999999999998</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="6">
+        <v>40</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" s="6">
+        <v>20</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>5</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D20" s="6">
+        <v>20</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20" s="1">
+        <v>9.1</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>6</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" s="6">
+        <v>20</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" s="1">
+        <v>15</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>7</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D22" s="6">
+        <v>20</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="1">
+        <v>2.41</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>8</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D23" s="6">
+        <v>20</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0.73</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="9">
+        <v>9</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D24" s="6">
+        <v>60</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" s="1">
+        <v>8.6</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" s="6">
+        <v>60</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D26" s="6">
+        <v>60</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D27" s="6">
+        <v>60</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D28" s="6">
+        <v>60</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="B14:B19"/>
+    <mergeCell ref="B24:B28"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="A24:A28"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>